--- a/frontend/public/templates/scores/v1/teaching-g23-admin-quality.xlsx
+++ b/frontend/public/templates/scores/v1/teaching-g23-admin-quality.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="R30c90d846bba4727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="Rcaceb36709ed4617"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,6 +348,10 @@
     <x:col min="28" max="28" width="16" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="16" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="16" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="16" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -372,12 +376,20 @@
         <x:v>标准差</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
+        <x:v>语文</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
+        <x:v>数学</x:v>
+      </x:c>
+      <x:c r="K1" s="8" t="str">
+        <x:v>英语</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
+        <x:v>三大门</x:v>
+      </x:c>
+      <x:c r="M1" s="8" t="str">
         <x:v>等级人数及比率</x:v>
       </x:c>
-      <x:c r="J1" s="8"/>
-      <x:c r="K1" s="8"/>
-      <x:c r="L1" s="8"/>
-      <x:c r="M1" s="8"/>
       <x:c r="N1" s="8"/>
       <x:c r="O1" s="8"/>
       <x:c r="P1" s="8"/>
@@ -395,6 +407,10 @@
       <x:c r="AB1" s="8"/>
       <x:c r="AC1" s="8"/>
       <x:c r="AD1" s="8"/>
+      <x:c r="AE1" s="8"/>
+      <x:c r="AF1" s="8"/>
+      <x:c r="AG1" s="8"/>
+      <x:c r="AH1" s="8"/>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8"/>
@@ -413,70 +429,74 @@
         <x:v>等级</x:v>
       </x:c>
       <x:c r="H2" s="8"/>
-      <x:c r="I2" s="8" t="str">
+      <x:c r="I2" s="8"/>
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8"/>
+      <x:c r="M2" s="8" t="str">
         <x:v>A+</x:v>
-      </x:c>
-      <x:c r="J2" s="8" t="str">
-        <x:v>比率</x:v>
-      </x:c>
-      <x:c r="K2" s="8" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="L2" s="8" t="str">
-        <x:v>比率</x:v>
-      </x:c>
-      <x:c r="M2" s="8" t="str">
-        <x:v>B+</x:v>
       </x:c>
       <x:c r="N2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="O2" s="8" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="P2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="Q2" s="8" t="str">
-        <x:v>B-</x:v>
+        <x:v>B+</x:v>
       </x:c>
       <x:c r="R2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="S2" s="8" t="str">
-        <x:v>C+</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="T2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="U2" s="8" t="str">
-        <x:v>C</x:v>
+        <x:v>B-</x:v>
       </x:c>
       <x:c r="V2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="W2" s="8" t="str">
-        <x:v>C-</x:v>
+        <x:v>C+</x:v>
       </x:c>
       <x:c r="X2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="Y2" s="8" t="str">
-        <x:v>D+</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str">
-        <x:v>D</x:v>
+        <x:v>C-</x:v>
       </x:c>
       <x:c r="AB2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="AC2" s="8" t="str">
+        <x:v>D+</x:v>
+      </x:c>
+      <x:c r="AD2" s="8" t="str">
+        <x:v>比率</x:v>
+      </x:c>
+      <x:c r="AE2" s="8" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="AF2" s="8" t="str">
+        <x:v>比率</x:v>
+      </x:c>
+      <x:c r="AG2" s="8" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="AD2" s="8" t="str">
+      <x:c r="AH2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
     </x:row>
@@ -489,10 +509,10 @@
       <x:c r="F3" s="14"/>
       <x:c r="G3" s="14"/>
       <x:c r="H3" s="14"/>
-      <x:c r="I3" s="13"/>
-      <x:c r="J3" s="15"/>
-      <x:c r="K3" s="13"/>
-      <x:c r="L3" s="15"/>
+      <x:c r="I3" s="14"/>
+      <x:c r="J3" s="14"/>
+      <x:c r="K3" s="14"/>
+      <x:c r="L3" s="14"/>
       <x:c r="M3" s="13"/>
       <x:c r="N3" s="15"/>
       <x:c r="O3" s="13"/>
@@ -511,6 +531,10 @@
       <x:c r="AB3" s="15"/>
       <x:c r="AC3" s="13"/>
       <x:c r="AD3" s="15"/>
+      <x:c r="AE3" s="13"/>
+      <x:c r="AF3" s="15"/>
+      <x:c r="AG3" s="13"/>
+      <x:c r="AH3" s="15"/>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="12"/>
@@ -521,10 +545,10 @@
       <x:c r="F4" s="14"/>
       <x:c r="G4" s="14"/>
       <x:c r="H4" s="14"/>
-      <x:c r="I4" s="13"/>
-      <x:c r="J4" s="15"/>
-      <x:c r="K4" s="13"/>
-      <x:c r="L4" s="15"/>
+      <x:c r="I4" s="14"/>
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="14"/>
+      <x:c r="L4" s="14"/>
       <x:c r="M4" s="13"/>
       <x:c r="N4" s="15"/>
       <x:c r="O4" s="13"/>
@@ -543,6 +567,10 @@
       <x:c r="AB4" s="15"/>
       <x:c r="AC4" s="13"/>
       <x:c r="AD4" s="15"/>
+      <x:c r="AE4" s="13"/>
+      <x:c r="AF4" s="15"/>
+      <x:c r="AG4" s="13"/>
+      <x:c r="AH4" s="15"/>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="12"/>
@@ -553,10 +581,10 @@
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
       <x:c r="H5" s="14"/>
-      <x:c r="I5" s="13"/>
-      <x:c r="J5" s="15"/>
-      <x:c r="K5" s="13"/>
-      <x:c r="L5" s="15"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5" s="14"/>
+      <x:c r="L5" s="14"/>
       <x:c r="M5" s="13"/>
       <x:c r="N5" s="15"/>
       <x:c r="O5" s="13"/>
@@ -575,6 +603,10 @@
       <x:c r="AB5" s="15"/>
       <x:c r="AC5" s="13"/>
       <x:c r="AD5" s="15"/>
+      <x:c r="AE5" s="13"/>
+      <x:c r="AF5" s="15"/>
+      <x:c r="AG5" s="13"/>
+      <x:c r="AH5" s="15"/>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="12"/>
@@ -585,10 +617,10 @@
       <x:c r="F6" s="14"/>
       <x:c r="G6" s="14"/>
       <x:c r="H6" s="14"/>
-      <x:c r="I6" s="13"/>
-      <x:c r="J6" s="15"/>
-      <x:c r="K6" s="13"/>
-      <x:c r="L6" s="15"/>
+      <x:c r="I6" s="14"/>
+      <x:c r="J6" s="14"/>
+      <x:c r="K6" s="14"/>
+      <x:c r="L6" s="14"/>
       <x:c r="M6" s="13"/>
       <x:c r="N6" s="15"/>
       <x:c r="O6" s="13"/>
@@ -607,6 +639,10 @@
       <x:c r="AB6" s="15"/>
       <x:c r="AC6" s="13"/>
       <x:c r="AD6" s="15"/>
+      <x:c r="AE6" s="13"/>
+      <x:c r="AF6" s="15"/>
+      <x:c r="AG6" s="13"/>
+      <x:c r="AH6" s="15"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="12"/>
@@ -617,10 +653,10 @@
       <x:c r="F7" s="14"/>
       <x:c r="G7" s="14"/>
       <x:c r="H7" s="14"/>
-      <x:c r="I7" s="13"/>
-      <x:c r="J7" s="15"/>
-      <x:c r="K7" s="13"/>
-      <x:c r="L7" s="15"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="14"/>
+      <x:c r="K7" s="14"/>
+      <x:c r="L7" s="14"/>
       <x:c r="M7" s="13"/>
       <x:c r="N7" s="15"/>
       <x:c r="O7" s="13"/>
@@ -639,6 +675,10 @@
       <x:c r="AB7" s="15"/>
       <x:c r="AC7" s="13"/>
       <x:c r="AD7" s="15"/>
+      <x:c r="AE7" s="13"/>
+      <x:c r="AF7" s="15"/>
+      <x:c r="AG7" s="13"/>
+      <x:c r="AH7" s="15"/>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="12"/>
@@ -649,10 +689,10 @@
       <x:c r="F8" s="14"/>
       <x:c r="G8" s="14"/>
       <x:c r="H8" s="14"/>
-      <x:c r="I8" s="13"/>
-      <x:c r="J8" s="15"/>
-      <x:c r="K8" s="13"/>
-      <x:c r="L8" s="15"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="J8" s="14"/>
+      <x:c r="K8" s="14"/>
+      <x:c r="L8" s="14"/>
       <x:c r="M8" s="13"/>
       <x:c r="N8" s="15"/>
       <x:c r="O8" s="13"/>
@@ -671,6 +711,10 @@
       <x:c r="AB8" s="15"/>
       <x:c r="AC8" s="13"/>
       <x:c r="AD8" s="15"/>
+      <x:c r="AE8" s="13"/>
+      <x:c r="AF8" s="15"/>
+      <x:c r="AG8" s="13"/>
+      <x:c r="AH8" s="15"/>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="12"/>
@@ -681,10 +725,10 @@
       <x:c r="F9" s="14"/>
       <x:c r="G9" s="14"/>
       <x:c r="H9" s="14"/>
-      <x:c r="I9" s="13"/>
-      <x:c r="J9" s="15"/>
-      <x:c r="K9" s="13"/>
-      <x:c r="L9" s="15"/>
+      <x:c r="I9" s="14"/>
+      <x:c r="J9" s="14"/>
+      <x:c r="K9" s="14"/>
+      <x:c r="L9" s="14"/>
       <x:c r="M9" s="13"/>
       <x:c r="N9" s="15"/>
       <x:c r="O9" s="13"/>
@@ -703,6 +747,10 @@
       <x:c r="AB9" s="15"/>
       <x:c r="AC9" s="13"/>
       <x:c r="AD9" s="15"/>
+      <x:c r="AE9" s="13"/>
+      <x:c r="AF9" s="15"/>
+      <x:c r="AG9" s="13"/>
+      <x:c r="AH9" s="15"/>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="12"/>
@@ -713,10 +761,10 @@
       <x:c r="F10" s="14"/>
       <x:c r="G10" s="14"/>
       <x:c r="H10" s="14"/>
-      <x:c r="I10" s="13"/>
-      <x:c r="J10" s="15"/>
-      <x:c r="K10" s="13"/>
-      <x:c r="L10" s="15"/>
+      <x:c r="I10" s="14"/>
+      <x:c r="J10" s="14"/>
+      <x:c r="K10" s="14"/>
+      <x:c r="L10" s="14"/>
       <x:c r="M10" s="13"/>
       <x:c r="N10" s="15"/>
       <x:c r="O10" s="13"/>
@@ -735,6 +783,10 @@
       <x:c r="AB10" s="15"/>
       <x:c r="AC10" s="13"/>
       <x:c r="AD10" s="15"/>
+      <x:c r="AE10" s="13"/>
+      <x:c r="AF10" s="15"/>
+      <x:c r="AG10" s="13"/>
+      <x:c r="AH10" s="15"/>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="12"/>
@@ -745,10 +797,10 @@
       <x:c r="F11" s="14"/>
       <x:c r="G11" s="14"/>
       <x:c r="H11" s="14"/>
-      <x:c r="I11" s="13"/>
-      <x:c r="J11" s="15"/>
-      <x:c r="K11" s="13"/>
-      <x:c r="L11" s="15"/>
+      <x:c r="I11" s="14"/>
+      <x:c r="J11" s="14"/>
+      <x:c r="K11" s="14"/>
+      <x:c r="L11" s="14"/>
       <x:c r="M11" s="13"/>
       <x:c r="N11" s="15"/>
       <x:c r="O11" s="13"/>
@@ -767,6 +819,10 @@
       <x:c r="AB11" s="15"/>
       <x:c r="AC11" s="13"/>
       <x:c r="AD11" s="15"/>
+      <x:c r="AE11" s="13"/>
+      <x:c r="AF11" s="15"/>
+      <x:c r="AG11" s="13"/>
+      <x:c r="AH11" s="15"/>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" s="12"/>
@@ -777,10 +833,10 @@
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14"/>
       <x:c r="H12" s="14"/>
-      <x:c r="I12" s="13"/>
-      <x:c r="J12" s="15"/>
-      <x:c r="K12" s="13"/>
-      <x:c r="L12" s="15"/>
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
+      <x:c r="K12" s="14"/>
+      <x:c r="L12" s="14"/>
       <x:c r="M12" s="13"/>
       <x:c r="N12" s="15"/>
       <x:c r="O12" s="13"/>
@@ -799,6 +855,10 @@
       <x:c r="AB12" s="15"/>
       <x:c r="AC12" s="13"/>
       <x:c r="AD12" s="15"/>
+      <x:c r="AE12" s="13"/>
+      <x:c r="AF12" s="15"/>
+      <x:c r="AG12" s="13"/>
+      <x:c r="AH12" s="15"/>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="12"/>
@@ -809,10 +869,10 @@
       <x:c r="F13" s="14"/>
       <x:c r="G13" s="14"/>
       <x:c r="H13" s="14"/>
-      <x:c r="I13" s="13"/>
-      <x:c r="J13" s="15"/>
-      <x:c r="K13" s="13"/>
-      <x:c r="L13" s="15"/>
+      <x:c r="I13" s="14"/>
+      <x:c r="J13" s="14"/>
+      <x:c r="K13" s="14"/>
+      <x:c r="L13" s="14"/>
       <x:c r="M13" s="13"/>
       <x:c r="N13" s="15"/>
       <x:c r="O13" s="13"/>
@@ -831,6 +891,10 @@
       <x:c r="AB13" s="15"/>
       <x:c r="AC13" s="13"/>
       <x:c r="AD13" s="15"/>
+      <x:c r="AE13" s="13"/>
+      <x:c r="AF13" s="15"/>
+      <x:c r="AG13" s="13"/>
+      <x:c r="AH13" s="15"/>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" s="12"/>
@@ -841,10 +905,10 @@
       <x:c r="F14" s="14"/>
       <x:c r="G14" s="14"/>
       <x:c r="H14" s="14"/>
-      <x:c r="I14" s="13"/>
-      <x:c r="J14" s="15"/>
-      <x:c r="K14" s="13"/>
-      <x:c r="L14" s="15"/>
+      <x:c r="I14" s="14"/>
+      <x:c r="J14" s="14"/>
+      <x:c r="K14" s="14"/>
+      <x:c r="L14" s="14"/>
       <x:c r="M14" s="13"/>
       <x:c r="N14" s="15"/>
       <x:c r="O14" s="13"/>
@@ -863,6 +927,10 @@
       <x:c r="AB14" s="15"/>
       <x:c r="AC14" s="13"/>
       <x:c r="AD14" s="15"/>
+      <x:c r="AE14" s="13"/>
+      <x:c r="AF14" s="15"/>
+      <x:c r="AG14" s="13"/>
+      <x:c r="AH14" s="15"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="12"/>
@@ -873,10 +941,10 @@
       <x:c r="F15" s="14"/>
       <x:c r="G15" s="14"/>
       <x:c r="H15" s="14"/>
-      <x:c r="I15" s="13"/>
-      <x:c r="J15" s="15"/>
-      <x:c r="K15" s="13"/>
-      <x:c r="L15" s="15"/>
+      <x:c r="I15" s="14"/>
+      <x:c r="J15" s="14"/>
+      <x:c r="K15" s="14"/>
+      <x:c r="L15" s="14"/>
       <x:c r="M15" s="13"/>
       <x:c r="N15" s="15"/>
       <x:c r="O15" s="13"/>
@@ -895,6 +963,10 @@
       <x:c r="AB15" s="15"/>
       <x:c r="AC15" s="13"/>
       <x:c r="AD15" s="15"/>
+      <x:c r="AE15" s="13"/>
+      <x:c r="AF15" s="15"/>
+      <x:c r="AG15" s="13"/>
+      <x:c r="AH15" s="15"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="12"/>
@@ -905,10 +977,10 @@
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14"/>
       <x:c r="H16" s="14"/>
-      <x:c r="I16" s="13"/>
-      <x:c r="J16" s="15"/>
-      <x:c r="K16" s="13"/>
-      <x:c r="L16" s="15"/>
+      <x:c r="I16" s="14"/>
+      <x:c r="J16" s="14"/>
+      <x:c r="K16" s="14"/>
+      <x:c r="L16" s="14"/>
       <x:c r="M16" s="13"/>
       <x:c r="N16" s="15"/>
       <x:c r="O16" s="13"/>
@@ -927,6 +999,10 @@
       <x:c r="AB16" s="15"/>
       <x:c r="AC16" s="13"/>
       <x:c r="AD16" s="15"/>
+      <x:c r="AE16" s="13"/>
+      <x:c r="AF16" s="15"/>
+      <x:c r="AG16" s="13"/>
+      <x:c r="AH16" s="15"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="12"/>
@@ -937,10 +1013,10 @@
       <x:c r="F17" s="14"/>
       <x:c r="G17" s="14"/>
       <x:c r="H17" s="14"/>
-      <x:c r="I17" s="13"/>
-      <x:c r="J17" s="15"/>
-      <x:c r="K17" s="13"/>
-      <x:c r="L17" s="15"/>
+      <x:c r="I17" s="14"/>
+      <x:c r="J17" s="14"/>
+      <x:c r="K17" s="14"/>
+      <x:c r="L17" s="14"/>
       <x:c r="M17" s="13"/>
       <x:c r="N17" s="15"/>
       <x:c r="O17" s="13"/>
@@ -959,6 +1035,10 @@
       <x:c r="AB17" s="15"/>
       <x:c r="AC17" s="13"/>
       <x:c r="AD17" s="15"/>
+      <x:c r="AE17" s="13"/>
+      <x:c r="AF17" s="15"/>
+      <x:c r="AG17" s="13"/>
+      <x:c r="AH17" s="15"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="12"/>
@@ -969,10 +1049,10 @@
       <x:c r="F18" s="14"/>
       <x:c r="G18" s="14"/>
       <x:c r="H18" s="14"/>
-      <x:c r="I18" s="13"/>
-      <x:c r="J18" s="15"/>
-      <x:c r="K18" s="13"/>
-      <x:c r="L18" s="15"/>
+      <x:c r="I18" s="14"/>
+      <x:c r="J18" s="14"/>
+      <x:c r="K18" s="14"/>
+      <x:c r="L18" s="14"/>
       <x:c r="M18" s="13"/>
       <x:c r="N18" s="15"/>
       <x:c r="O18" s="13"/>
@@ -991,6 +1071,10 @@
       <x:c r="AB18" s="15"/>
       <x:c r="AC18" s="13"/>
       <x:c r="AD18" s="15"/>
+      <x:c r="AE18" s="13"/>
+      <x:c r="AF18" s="15"/>
+      <x:c r="AG18" s="13"/>
+      <x:c r="AH18" s="15"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="12"/>
@@ -1001,10 +1085,10 @@
       <x:c r="F19" s="14"/>
       <x:c r="G19" s="14"/>
       <x:c r="H19" s="14"/>
-      <x:c r="I19" s="13"/>
-      <x:c r="J19" s="15"/>
-      <x:c r="K19" s="13"/>
-      <x:c r="L19" s="15"/>
+      <x:c r="I19" s="14"/>
+      <x:c r="J19" s="14"/>
+      <x:c r="K19" s="14"/>
+      <x:c r="L19" s="14"/>
       <x:c r="M19" s="13"/>
       <x:c r="N19" s="15"/>
       <x:c r="O19" s="13"/>
@@ -1023,6 +1107,10 @@
       <x:c r="AB19" s="15"/>
       <x:c r="AC19" s="13"/>
       <x:c r="AD19" s="15"/>
+      <x:c r="AE19" s="13"/>
+      <x:c r="AF19" s="15"/>
+      <x:c r="AG19" s="13"/>
+      <x:c r="AH19" s="15"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="12"/>
@@ -1033,10 +1121,10 @@
       <x:c r="F20" s="14"/>
       <x:c r="G20" s="14"/>
       <x:c r="H20" s="14"/>
-      <x:c r="I20" s="13"/>
-      <x:c r="J20" s="15"/>
-      <x:c r="K20" s="13"/>
-      <x:c r="L20" s="15"/>
+      <x:c r="I20" s="14"/>
+      <x:c r="J20" s="14"/>
+      <x:c r="K20" s="14"/>
+      <x:c r="L20" s="14"/>
       <x:c r="M20" s="13"/>
       <x:c r="N20" s="15"/>
       <x:c r="O20" s="13"/>
@@ -1055,6 +1143,10 @@
       <x:c r="AB20" s="15"/>
       <x:c r="AC20" s="13"/>
       <x:c r="AD20" s="15"/>
+      <x:c r="AE20" s="13"/>
+      <x:c r="AF20" s="15"/>
+      <x:c r="AG20" s="13"/>
+      <x:c r="AH20" s="15"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="12"/>
@@ -1065,10 +1157,10 @@
       <x:c r="F21" s="14"/>
       <x:c r="G21" s="14"/>
       <x:c r="H21" s="14"/>
-      <x:c r="I21" s="13"/>
-      <x:c r="J21" s="15"/>
-      <x:c r="K21" s="13"/>
-      <x:c r="L21" s="15"/>
+      <x:c r="I21" s="14"/>
+      <x:c r="J21" s="14"/>
+      <x:c r="K21" s="14"/>
+      <x:c r="L21" s="14"/>
       <x:c r="M21" s="13"/>
       <x:c r="N21" s="15"/>
       <x:c r="O21" s="13"/>
@@ -1087,6 +1179,10 @@
       <x:c r="AB21" s="15"/>
       <x:c r="AC21" s="13"/>
       <x:c r="AD21" s="15"/>
+      <x:c r="AE21" s="13"/>
+      <x:c r="AF21" s="15"/>
+      <x:c r="AG21" s="13"/>
+      <x:c r="AH21" s="15"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="12"/>
@@ -1097,10 +1193,10 @@
       <x:c r="F22" s="14"/>
       <x:c r="G22" s="14"/>
       <x:c r="H22" s="14"/>
-      <x:c r="I22" s="13"/>
-      <x:c r="J22" s="15"/>
-      <x:c r="K22" s="13"/>
-      <x:c r="L22" s="15"/>
+      <x:c r="I22" s="14"/>
+      <x:c r="J22" s="14"/>
+      <x:c r="K22" s="14"/>
+      <x:c r="L22" s="14"/>
       <x:c r="M22" s="13"/>
       <x:c r="N22" s="15"/>
       <x:c r="O22" s="13"/>
@@ -1119,6 +1215,10 @@
       <x:c r="AB22" s="15"/>
       <x:c r="AC22" s="13"/>
       <x:c r="AD22" s="15"/>
+      <x:c r="AE22" s="13"/>
+      <x:c r="AF22" s="15"/>
+      <x:c r="AG22" s="13"/>
+      <x:c r="AH22" s="15"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="12"/>
@@ -1129,10 +1229,10 @@
       <x:c r="F23" s="14"/>
       <x:c r="G23" s="14"/>
       <x:c r="H23" s="14"/>
-      <x:c r="I23" s="13"/>
-      <x:c r="J23" s="15"/>
-      <x:c r="K23" s="13"/>
-      <x:c r="L23" s="15"/>
+      <x:c r="I23" s="14"/>
+      <x:c r="J23" s="14"/>
+      <x:c r="K23" s="14"/>
+      <x:c r="L23" s="14"/>
       <x:c r="M23" s="13"/>
       <x:c r="N23" s="15"/>
       <x:c r="O23" s="13"/>
@@ -1151,6 +1251,10 @@
       <x:c r="AB23" s="15"/>
       <x:c r="AC23" s="13"/>
       <x:c r="AD23" s="15"/>
+      <x:c r="AE23" s="13"/>
+      <x:c r="AF23" s="15"/>
+      <x:c r="AG23" s="13"/>
+      <x:c r="AH23" s="15"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="12"/>
@@ -1161,10 +1265,10 @@
       <x:c r="F24" s="14"/>
       <x:c r="G24" s="14"/>
       <x:c r="H24" s="14"/>
-      <x:c r="I24" s="13"/>
-      <x:c r="J24" s="15"/>
-      <x:c r="K24" s="13"/>
-      <x:c r="L24" s="15"/>
+      <x:c r="I24" s="14"/>
+      <x:c r="J24" s="14"/>
+      <x:c r="K24" s="14"/>
+      <x:c r="L24" s="14"/>
       <x:c r="M24" s="13"/>
       <x:c r="N24" s="15"/>
       <x:c r="O24" s="13"/>
@@ -1183,6 +1287,10 @@
       <x:c r="AB24" s="15"/>
       <x:c r="AC24" s="13"/>
       <x:c r="AD24" s="15"/>
+      <x:c r="AE24" s="13"/>
+      <x:c r="AF24" s="15"/>
+      <x:c r="AG24" s="13"/>
+      <x:c r="AH24" s="15"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="12"/>
@@ -1193,10 +1301,10 @@
       <x:c r="F25" s="14"/>
       <x:c r="G25" s="14"/>
       <x:c r="H25" s="14"/>
-      <x:c r="I25" s="13"/>
-      <x:c r="J25" s="15"/>
-      <x:c r="K25" s="13"/>
-      <x:c r="L25" s="15"/>
+      <x:c r="I25" s="14"/>
+      <x:c r="J25" s="14"/>
+      <x:c r="K25" s="14"/>
+      <x:c r="L25" s="14"/>
       <x:c r="M25" s="13"/>
       <x:c r="N25" s="15"/>
       <x:c r="O25" s="13"/>
@@ -1215,6 +1323,10 @@
       <x:c r="AB25" s="15"/>
       <x:c r="AC25" s="13"/>
       <x:c r="AD25" s="15"/>
+      <x:c r="AE25" s="13"/>
+      <x:c r="AF25" s="15"/>
+      <x:c r="AG25" s="13"/>
+      <x:c r="AH25" s="15"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="12"/>
@@ -1225,10 +1337,10 @@
       <x:c r="F26" s="14"/>
       <x:c r="G26" s="14"/>
       <x:c r="H26" s="14"/>
-      <x:c r="I26" s="13"/>
-      <x:c r="J26" s="15"/>
-      <x:c r="K26" s="13"/>
-      <x:c r="L26" s="15"/>
+      <x:c r="I26" s="14"/>
+      <x:c r="J26" s="14"/>
+      <x:c r="K26" s="14"/>
+      <x:c r="L26" s="14"/>
       <x:c r="M26" s="13"/>
       <x:c r="N26" s="15"/>
       <x:c r="O26" s="13"/>
@@ -1247,6 +1359,10 @@
       <x:c r="AB26" s="15"/>
       <x:c r="AC26" s="13"/>
       <x:c r="AD26" s="15"/>
+      <x:c r="AE26" s="13"/>
+      <x:c r="AF26" s="15"/>
+      <x:c r="AG26" s="13"/>
+      <x:c r="AH26" s="15"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="12"/>
@@ -1257,10 +1373,10 @@
       <x:c r="F27" s="14"/>
       <x:c r="G27" s="14"/>
       <x:c r="H27" s="14"/>
-      <x:c r="I27" s="13"/>
-      <x:c r="J27" s="15"/>
-      <x:c r="K27" s="13"/>
-      <x:c r="L27" s="15"/>
+      <x:c r="I27" s="14"/>
+      <x:c r="J27" s="14"/>
+      <x:c r="K27" s="14"/>
+      <x:c r="L27" s="14"/>
       <x:c r="M27" s="13"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="13"/>
@@ -1279,6 +1395,10 @@
       <x:c r="AB27" s="15"/>
       <x:c r="AC27" s="13"/>
       <x:c r="AD27" s="15"/>
+      <x:c r="AE27" s="13"/>
+      <x:c r="AF27" s="15"/>
+      <x:c r="AG27" s="13"/>
+      <x:c r="AH27" s="15"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="12"/>
@@ -1289,10 +1409,10 @@
       <x:c r="F28" s="14"/>
       <x:c r="G28" s="14"/>
       <x:c r="H28" s="14"/>
-      <x:c r="I28" s="13"/>
-      <x:c r="J28" s="15"/>
-      <x:c r="K28" s="13"/>
-      <x:c r="L28" s="15"/>
+      <x:c r="I28" s="14"/>
+      <x:c r="J28" s="14"/>
+      <x:c r="K28" s="14"/>
+      <x:c r="L28" s="14"/>
       <x:c r="M28" s="13"/>
       <x:c r="N28" s="15"/>
       <x:c r="O28" s="13"/>
@@ -1311,6 +1431,10 @@
       <x:c r="AB28" s="15"/>
       <x:c r="AC28" s="13"/>
       <x:c r="AD28" s="15"/>
+      <x:c r="AE28" s="13"/>
+      <x:c r="AF28" s="15"/>
+      <x:c r="AG28" s="13"/>
+      <x:c r="AH28" s="15"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="12"/>
@@ -1321,10 +1445,10 @@
       <x:c r="F29" s="14"/>
       <x:c r="G29" s="14"/>
       <x:c r="H29" s="14"/>
-      <x:c r="I29" s="13"/>
-      <x:c r="J29" s="15"/>
-      <x:c r="K29" s="13"/>
-      <x:c r="L29" s="15"/>
+      <x:c r="I29" s="14"/>
+      <x:c r="J29" s="14"/>
+      <x:c r="K29" s="14"/>
+      <x:c r="L29" s="14"/>
       <x:c r="M29" s="13"/>
       <x:c r="N29" s="15"/>
       <x:c r="O29" s="13"/>
@@ -1343,6 +1467,10 @@
       <x:c r="AB29" s="15"/>
       <x:c r="AC29" s="13"/>
       <x:c r="AD29" s="15"/>
+      <x:c r="AE29" s="13"/>
+      <x:c r="AF29" s="15"/>
+      <x:c r="AG29" s="13"/>
+      <x:c r="AH29" s="15"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="12"/>
@@ -1353,10 +1481,10 @@
       <x:c r="F30" s="14"/>
       <x:c r="G30" s="14"/>
       <x:c r="H30" s="14"/>
-      <x:c r="I30" s="13"/>
-      <x:c r="J30" s="15"/>
-      <x:c r="K30" s="13"/>
-      <x:c r="L30" s="15"/>
+      <x:c r="I30" s="14"/>
+      <x:c r="J30" s="14"/>
+      <x:c r="K30" s="14"/>
+      <x:c r="L30" s="14"/>
       <x:c r="M30" s="13"/>
       <x:c r="N30" s="15"/>
       <x:c r="O30" s="13"/>
@@ -1375,6 +1503,10 @@
       <x:c r="AB30" s="15"/>
       <x:c r="AC30" s="13"/>
       <x:c r="AD30" s="15"/>
+      <x:c r="AE30" s="13"/>
+      <x:c r="AF30" s="15"/>
+      <x:c r="AG30" s="13"/>
+      <x:c r="AH30" s="15"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="12"/>
@@ -1385,10 +1517,10 @@
       <x:c r="F31" s="14"/>
       <x:c r="G31" s="14"/>
       <x:c r="H31" s="14"/>
-      <x:c r="I31" s="13"/>
-      <x:c r="J31" s="15"/>
-      <x:c r="K31" s="13"/>
-      <x:c r="L31" s="15"/>
+      <x:c r="I31" s="14"/>
+      <x:c r="J31" s="14"/>
+      <x:c r="K31" s="14"/>
+      <x:c r="L31" s="14"/>
       <x:c r="M31" s="13"/>
       <x:c r="N31" s="15"/>
       <x:c r="O31" s="13"/>
@@ -1407,6 +1539,10 @@
       <x:c r="AB31" s="15"/>
       <x:c r="AC31" s="13"/>
       <x:c r="AD31" s="15"/>
+      <x:c r="AE31" s="13"/>
+      <x:c r="AF31" s="15"/>
+      <x:c r="AG31" s="13"/>
+      <x:c r="AH31" s="15"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="12"/>
@@ -1417,10 +1553,10 @@
       <x:c r="F32" s="14"/>
       <x:c r="G32" s="14"/>
       <x:c r="H32" s="14"/>
-      <x:c r="I32" s="13"/>
-      <x:c r="J32" s="15"/>
-      <x:c r="K32" s="13"/>
-      <x:c r="L32" s="15"/>
+      <x:c r="I32" s="14"/>
+      <x:c r="J32" s="14"/>
+      <x:c r="K32" s="14"/>
+      <x:c r="L32" s="14"/>
       <x:c r="M32" s="13"/>
       <x:c r="N32" s="15"/>
       <x:c r="O32" s="13"/>
@@ -1439,6 +1575,10 @@
       <x:c r="AB32" s="15"/>
       <x:c r="AC32" s="13"/>
       <x:c r="AD32" s="15"/>
+      <x:c r="AE32" s="13"/>
+      <x:c r="AF32" s="15"/>
+      <x:c r="AG32" s="13"/>
+      <x:c r="AH32" s="15"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="12"/>
@@ -1449,10 +1589,10 @@
       <x:c r="F33" s="14"/>
       <x:c r="G33" s="14"/>
       <x:c r="H33" s="14"/>
-      <x:c r="I33" s="13"/>
-      <x:c r="J33" s="15"/>
-      <x:c r="K33" s="13"/>
-      <x:c r="L33" s="15"/>
+      <x:c r="I33" s="14"/>
+      <x:c r="J33" s="14"/>
+      <x:c r="K33" s="14"/>
+      <x:c r="L33" s="14"/>
       <x:c r="M33" s="13"/>
       <x:c r="N33" s="15"/>
       <x:c r="O33" s="13"/>
@@ -1471,6 +1611,10 @@
       <x:c r="AB33" s="15"/>
       <x:c r="AC33" s="13"/>
       <x:c r="AD33" s="15"/>
+      <x:c r="AE33" s="13"/>
+      <x:c r="AF33" s="15"/>
+      <x:c r="AG33" s="13"/>
+      <x:c r="AH33" s="15"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="12"/>
@@ -1481,10 +1625,10 @@
       <x:c r="F34" s="14"/>
       <x:c r="G34" s="14"/>
       <x:c r="H34" s="14"/>
-      <x:c r="I34" s="13"/>
-      <x:c r="J34" s="15"/>
-      <x:c r="K34" s="13"/>
-      <x:c r="L34" s="15"/>
+      <x:c r="I34" s="14"/>
+      <x:c r="J34" s="14"/>
+      <x:c r="K34" s="14"/>
+      <x:c r="L34" s="14"/>
       <x:c r="M34" s="13"/>
       <x:c r="N34" s="15"/>
       <x:c r="O34" s="13"/>
@@ -1503,6 +1647,10 @@
       <x:c r="AB34" s="15"/>
       <x:c r="AC34" s="13"/>
       <x:c r="AD34" s="15"/>
+      <x:c r="AE34" s="13"/>
+      <x:c r="AF34" s="15"/>
+      <x:c r="AG34" s="13"/>
+      <x:c r="AH34" s="15"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="12"/>
@@ -1513,10 +1661,10 @@
       <x:c r="F35" s="14"/>
       <x:c r="G35" s="14"/>
       <x:c r="H35" s="14"/>
-      <x:c r="I35" s="13"/>
-      <x:c r="J35" s="15"/>
-      <x:c r="K35" s="13"/>
-      <x:c r="L35" s="15"/>
+      <x:c r="I35" s="14"/>
+      <x:c r="J35" s="14"/>
+      <x:c r="K35" s="14"/>
+      <x:c r="L35" s="14"/>
       <x:c r="M35" s="13"/>
       <x:c r="N35" s="15"/>
       <x:c r="O35" s="13"/>
@@ -1535,6 +1683,10 @@
       <x:c r="AB35" s="15"/>
       <x:c r="AC35" s="13"/>
       <x:c r="AD35" s="15"/>
+      <x:c r="AE35" s="13"/>
+      <x:c r="AF35" s="15"/>
+      <x:c r="AG35" s="13"/>
+      <x:c r="AH35" s="15"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
       <x:c r="A36" s="12"/>
@@ -1545,10 +1697,10 @@
       <x:c r="F36" s="14"/>
       <x:c r="G36" s="14"/>
       <x:c r="H36" s="14"/>
-      <x:c r="I36" s="13"/>
-      <x:c r="J36" s="15"/>
-      <x:c r="K36" s="13"/>
-      <x:c r="L36" s="15"/>
+      <x:c r="I36" s="14"/>
+      <x:c r="J36" s="14"/>
+      <x:c r="K36" s="14"/>
+      <x:c r="L36" s="14"/>
       <x:c r="M36" s="13"/>
       <x:c r="N36" s="15"/>
       <x:c r="O36" s="13"/>
@@ -1567,6 +1719,10 @@
       <x:c r="AB36" s="15"/>
       <x:c r="AC36" s="13"/>
       <x:c r="AD36" s="15"/>
+      <x:c r="AE36" s="13"/>
+      <x:c r="AF36" s="15"/>
+      <x:c r="AG36" s="13"/>
+      <x:c r="AH36" s="15"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="12"/>
@@ -1577,10 +1733,10 @@
       <x:c r="F37" s="14"/>
       <x:c r="G37" s="14"/>
       <x:c r="H37" s="14"/>
-      <x:c r="I37" s="13"/>
-      <x:c r="J37" s="15"/>
-      <x:c r="K37" s="13"/>
-      <x:c r="L37" s="15"/>
+      <x:c r="I37" s="14"/>
+      <x:c r="J37" s="14"/>
+      <x:c r="K37" s="14"/>
+      <x:c r="L37" s="14"/>
       <x:c r="M37" s="13"/>
       <x:c r="N37" s="15"/>
       <x:c r="O37" s="13"/>
@@ -1599,6 +1755,10 @@
       <x:c r="AB37" s="15"/>
       <x:c r="AC37" s="13"/>
       <x:c r="AD37" s="15"/>
+      <x:c r="AE37" s="13"/>
+      <x:c r="AF37" s="15"/>
+      <x:c r="AG37" s="13"/>
+      <x:c r="AH37" s="15"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="12"/>
@@ -1609,10 +1769,10 @@
       <x:c r="F38" s="14"/>
       <x:c r="G38" s="14"/>
       <x:c r="H38" s="14"/>
-      <x:c r="I38" s="13"/>
-      <x:c r="J38" s="15"/>
-      <x:c r="K38" s="13"/>
-      <x:c r="L38" s="15"/>
+      <x:c r="I38" s="14"/>
+      <x:c r="J38" s="14"/>
+      <x:c r="K38" s="14"/>
+      <x:c r="L38" s="14"/>
       <x:c r="M38" s="13"/>
       <x:c r="N38" s="15"/>
       <x:c r="O38" s="13"/>
@@ -1631,6 +1791,10 @@
       <x:c r="AB38" s="15"/>
       <x:c r="AC38" s="13"/>
       <x:c r="AD38" s="15"/>
+      <x:c r="AE38" s="13"/>
+      <x:c r="AF38" s="15"/>
+      <x:c r="AG38" s="13"/>
+      <x:c r="AH38" s="15"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="12"/>
@@ -1641,10 +1805,10 @@
       <x:c r="F39" s="14"/>
       <x:c r="G39" s="14"/>
       <x:c r="H39" s="14"/>
-      <x:c r="I39" s="13"/>
-      <x:c r="J39" s="15"/>
-      <x:c r="K39" s="13"/>
-      <x:c r="L39" s="15"/>
+      <x:c r="I39" s="14"/>
+      <x:c r="J39" s="14"/>
+      <x:c r="K39" s="14"/>
+      <x:c r="L39" s="14"/>
       <x:c r="M39" s="13"/>
       <x:c r="N39" s="15"/>
       <x:c r="O39" s="13"/>
@@ -1663,6 +1827,10 @@
       <x:c r="AB39" s="15"/>
       <x:c r="AC39" s="13"/>
       <x:c r="AD39" s="15"/>
+      <x:c r="AE39" s="13"/>
+      <x:c r="AF39" s="15"/>
+      <x:c r="AG39" s="13"/>
+      <x:c r="AH39" s="15"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="12"/>
@@ -1673,10 +1841,10 @@
       <x:c r="F40" s="14"/>
       <x:c r="G40" s="14"/>
       <x:c r="H40" s="14"/>
-      <x:c r="I40" s="13"/>
-      <x:c r="J40" s="15"/>
-      <x:c r="K40" s="13"/>
-      <x:c r="L40" s="15"/>
+      <x:c r="I40" s="14"/>
+      <x:c r="J40" s="14"/>
+      <x:c r="K40" s="14"/>
+      <x:c r="L40" s="14"/>
       <x:c r="M40" s="13"/>
       <x:c r="N40" s="15"/>
       <x:c r="O40" s="13"/>
@@ -1695,6 +1863,10 @@
       <x:c r="AB40" s="15"/>
       <x:c r="AC40" s="13"/>
       <x:c r="AD40" s="15"/>
+      <x:c r="AE40" s="13"/>
+      <x:c r="AF40" s="15"/>
+      <x:c r="AG40" s="13"/>
+      <x:c r="AH40" s="15"/>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
       <x:c r="A41" s="12"/>
@@ -1705,10 +1877,10 @@
       <x:c r="F41" s="14"/>
       <x:c r="G41" s="14"/>
       <x:c r="H41" s="14"/>
-      <x:c r="I41" s="13"/>
-      <x:c r="J41" s="15"/>
-      <x:c r="K41" s="13"/>
-      <x:c r="L41" s="15"/>
+      <x:c r="I41" s="14"/>
+      <x:c r="J41" s="14"/>
+      <x:c r="K41" s="14"/>
+      <x:c r="L41" s="14"/>
       <x:c r="M41" s="13"/>
       <x:c r="N41" s="15"/>
       <x:c r="O41" s="13"/>
@@ -1727,6 +1899,10 @@
       <x:c r="AB41" s="15"/>
       <x:c r="AC41" s="13"/>
       <x:c r="AD41" s="15"/>
+      <x:c r="AE41" s="13"/>
+      <x:c r="AF41" s="15"/>
+      <x:c r="AG41" s="13"/>
+      <x:c r="AH41" s="15"/>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
       <x:c r="A42" s="12"/>
@@ -1737,10 +1913,10 @@
       <x:c r="F42" s="14"/>
       <x:c r="G42" s="14"/>
       <x:c r="H42" s="14"/>
-      <x:c r="I42" s="13"/>
-      <x:c r="J42" s="15"/>
-      <x:c r="K42" s="13"/>
-      <x:c r="L42" s="15"/>
+      <x:c r="I42" s="14"/>
+      <x:c r="J42" s="14"/>
+      <x:c r="K42" s="14"/>
+      <x:c r="L42" s="14"/>
       <x:c r="M42" s="13"/>
       <x:c r="N42" s="15"/>
       <x:c r="O42" s="13"/>
@@ -1759,6 +1935,10 @@
       <x:c r="AB42" s="15"/>
       <x:c r="AC42" s="13"/>
       <x:c r="AD42" s="15"/>
+      <x:c r="AE42" s="13"/>
+      <x:c r="AF42" s="15"/>
+      <x:c r="AG42" s="13"/>
+      <x:c r="AH42" s="15"/>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
       <x:c r="A43" s="12"/>
@@ -1769,10 +1949,10 @@
       <x:c r="F43" s="14"/>
       <x:c r="G43" s="14"/>
       <x:c r="H43" s="14"/>
-      <x:c r="I43" s="13"/>
-      <x:c r="J43" s="15"/>
-      <x:c r="K43" s="13"/>
-      <x:c r="L43" s="15"/>
+      <x:c r="I43" s="14"/>
+      <x:c r="J43" s="14"/>
+      <x:c r="K43" s="14"/>
+      <x:c r="L43" s="14"/>
       <x:c r="M43" s="13"/>
       <x:c r="N43" s="15"/>
       <x:c r="O43" s="13"/>
@@ -1791,6 +1971,10 @@
       <x:c r="AB43" s="15"/>
       <x:c r="AC43" s="13"/>
       <x:c r="AD43" s="15"/>
+      <x:c r="AE43" s="13"/>
+      <x:c r="AF43" s="15"/>
+      <x:c r="AG43" s="13"/>
+      <x:c r="AH43" s="15"/>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
       <x:c r="A44" s="12"/>
@@ -1801,10 +1985,10 @@
       <x:c r="F44" s="14"/>
       <x:c r="G44" s="14"/>
       <x:c r="H44" s="14"/>
-      <x:c r="I44" s="13"/>
-      <x:c r="J44" s="15"/>
-      <x:c r="K44" s="13"/>
-      <x:c r="L44" s="15"/>
+      <x:c r="I44" s="14"/>
+      <x:c r="J44" s="14"/>
+      <x:c r="K44" s="14"/>
+      <x:c r="L44" s="14"/>
       <x:c r="M44" s="13"/>
       <x:c r="N44" s="15"/>
       <x:c r="O44" s="13"/>
@@ -1823,6 +2007,10 @@
       <x:c r="AB44" s="15"/>
       <x:c r="AC44" s="13"/>
       <x:c r="AD44" s="15"/>
+      <x:c r="AE44" s="13"/>
+      <x:c r="AF44" s="15"/>
+      <x:c r="AG44" s="13"/>
+      <x:c r="AH44" s="15"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
       <x:c r="A45" s="12"/>
@@ -1833,10 +2021,10 @@
       <x:c r="F45" s="14"/>
       <x:c r="G45" s="14"/>
       <x:c r="H45" s="14"/>
-      <x:c r="I45" s="13"/>
-      <x:c r="J45" s="15"/>
-      <x:c r="K45" s="13"/>
-      <x:c r="L45" s="15"/>
+      <x:c r="I45" s="14"/>
+      <x:c r="J45" s="14"/>
+      <x:c r="K45" s="14"/>
+      <x:c r="L45" s="14"/>
       <x:c r="M45" s="13"/>
       <x:c r="N45" s="15"/>
       <x:c r="O45" s="13"/>
@@ -1855,6 +2043,10 @@
       <x:c r="AB45" s="15"/>
       <x:c r="AC45" s="13"/>
       <x:c r="AD45" s="15"/>
+      <x:c r="AE45" s="13"/>
+      <x:c r="AF45" s="15"/>
+      <x:c r="AG45" s="13"/>
+      <x:c r="AH45" s="15"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
       <x:c r="A46" s="12"/>
@@ -1865,10 +2057,10 @@
       <x:c r="F46" s="14"/>
       <x:c r="G46" s="14"/>
       <x:c r="H46" s="14"/>
-      <x:c r="I46" s="13"/>
-      <x:c r="J46" s="15"/>
-      <x:c r="K46" s="13"/>
-      <x:c r="L46" s="15"/>
+      <x:c r="I46" s="14"/>
+      <x:c r="J46" s="14"/>
+      <x:c r="K46" s="14"/>
+      <x:c r="L46" s="14"/>
       <x:c r="M46" s="13"/>
       <x:c r="N46" s="15"/>
       <x:c r="O46" s="13"/>
@@ -1887,6 +2079,10 @@
       <x:c r="AB46" s="15"/>
       <x:c r="AC46" s="13"/>
       <x:c r="AD46" s="15"/>
+      <x:c r="AE46" s="13"/>
+      <x:c r="AF46" s="15"/>
+      <x:c r="AG46" s="13"/>
+      <x:c r="AH46" s="15"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
       <x:c r="A47" s="12"/>
@@ -1897,10 +2093,10 @@
       <x:c r="F47" s="14"/>
       <x:c r="G47" s="14"/>
       <x:c r="H47" s="14"/>
-      <x:c r="I47" s="13"/>
-      <x:c r="J47" s="15"/>
-      <x:c r="K47" s="13"/>
-      <x:c r="L47" s="15"/>
+      <x:c r="I47" s="14"/>
+      <x:c r="J47" s="14"/>
+      <x:c r="K47" s="14"/>
+      <x:c r="L47" s="14"/>
       <x:c r="M47" s="13"/>
       <x:c r="N47" s="15"/>
       <x:c r="O47" s="13"/>
@@ -1919,6 +2115,10 @@
       <x:c r="AB47" s="15"/>
       <x:c r="AC47" s="13"/>
       <x:c r="AD47" s="15"/>
+      <x:c r="AE47" s="13"/>
+      <x:c r="AF47" s="15"/>
+      <x:c r="AG47" s="13"/>
+      <x:c r="AH47" s="15"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
       <x:c r="A48" s="12"/>
@@ -1929,10 +2129,10 @@
       <x:c r="F48" s="14"/>
       <x:c r="G48" s="14"/>
       <x:c r="H48" s="14"/>
-      <x:c r="I48" s="13"/>
-      <x:c r="J48" s="15"/>
-      <x:c r="K48" s="13"/>
-      <x:c r="L48" s="15"/>
+      <x:c r="I48" s="14"/>
+      <x:c r="J48" s="14"/>
+      <x:c r="K48" s="14"/>
+      <x:c r="L48" s="14"/>
       <x:c r="M48" s="13"/>
       <x:c r="N48" s="15"/>
       <x:c r="O48" s="13"/>
@@ -1951,6 +2151,10 @@
       <x:c r="AB48" s="15"/>
       <x:c r="AC48" s="13"/>
       <x:c r="AD48" s="15"/>
+      <x:c r="AE48" s="13"/>
+      <x:c r="AF48" s="15"/>
+      <x:c r="AG48" s="13"/>
+      <x:c r="AH48" s="15"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
       <x:c r="A49" s="12"/>
@@ -1961,10 +2165,10 @@
       <x:c r="F49" s="14"/>
       <x:c r="G49" s="14"/>
       <x:c r="H49" s="14"/>
-      <x:c r="I49" s="13"/>
-      <x:c r="J49" s="15"/>
-      <x:c r="K49" s="13"/>
-      <x:c r="L49" s="15"/>
+      <x:c r="I49" s="14"/>
+      <x:c r="J49" s="14"/>
+      <x:c r="K49" s="14"/>
+      <x:c r="L49" s="14"/>
       <x:c r="M49" s="13"/>
       <x:c r="N49" s="15"/>
       <x:c r="O49" s="13"/>
@@ -1983,6 +2187,10 @@
       <x:c r="AB49" s="15"/>
       <x:c r="AC49" s="13"/>
       <x:c r="AD49" s="15"/>
+      <x:c r="AE49" s="13"/>
+      <x:c r="AF49" s="15"/>
+      <x:c r="AG49" s="13"/>
+      <x:c r="AH49" s="15"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
       <x:c r="A50" s="12"/>
@@ -1993,10 +2201,10 @@
       <x:c r="F50" s="14"/>
       <x:c r="G50" s="14"/>
       <x:c r="H50" s="14"/>
-      <x:c r="I50" s="13"/>
-      <x:c r="J50" s="15"/>
-      <x:c r="K50" s="13"/>
-      <x:c r="L50" s="15"/>
+      <x:c r="I50" s="14"/>
+      <x:c r="J50" s="14"/>
+      <x:c r="K50" s="14"/>
+      <x:c r="L50" s="14"/>
       <x:c r="M50" s="13"/>
       <x:c r="N50" s="15"/>
       <x:c r="O50" s="13"/>
@@ -2015,6 +2223,10 @@
       <x:c r="AB50" s="15"/>
       <x:c r="AC50" s="13"/>
       <x:c r="AD50" s="15"/>
+      <x:c r="AE50" s="13"/>
+      <x:c r="AF50" s="15"/>
+      <x:c r="AG50" s="13"/>
+      <x:c r="AH50" s="15"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
       <x:c r="A51" s="12"/>
@@ -2025,10 +2237,10 @@
       <x:c r="F51" s="14"/>
       <x:c r="G51" s="14"/>
       <x:c r="H51" s="14"/>
-      <x:c r="I51" s="13"/>
-      <x:c r="J51" s="15"/>
-      <x:c r="K51" s="13"/>
-      <x:c r="L51" s="15"/>
+      <x:c r="I51" s="14"/>
+      <x:c r="J51" s="14"/>
+      <x:c r="K51" s="14"/>
+      <x:c r="L51" s="14"/>
       <x:c r="M51" s="13"/>
       <x:c r="N51" s="15"/>
       <x:c r="O51" s="13"/>
@@ -2047,6 +2259,10 @@
       <x:c r="AB51" s="15"/>
       <x:c r="AC51" s="13"/>
       <x:c r="AD51" s="15"/>
+      <x:c r="AE51" s="13"/>
+      <x:c r="AF51" s="15"/>
+      <x:c r="AG51" s="13"/>
+      <x:c r="AH51" s="15"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
       <x:c r="A52" s="12"/>
@@ -2057,10 +2273,10 @@
       <x:c r="F52" s="14"/>
       <x:c r="G52" s="14"/>
       <x:c r="H52" s="14"/>
-      <x:c r="I52" s="13"/>
-      <x:c r="J52" s="15"/>
-      <x:c r="K52" s="13"/>
-      <x:c r="L52" s="15"/>
+      <x:c r="I52" s="14"/>
+      <x:c r="J52" s="14"/>
+      <x:c r="K52" s="14"/>
+      <x:c r="L52" s="14"/>
       <x:c r="M52" s="13"/>
       <x:c r="N52" s="15"/>
       <x:c r="O52" s="13"/>
@@ -2079,6 +2295,10 @@
       <x:c r="AB52" s="15"/>
       <x:c r="AC52" s="13"/>
       <x:c r="AD52" s="15"/>
+      <x:c r="AE52" s="13"/>
+      <x:c r="AF52" s="15"/>
+      <x:c r="AG52" s="13"/>
+      <x:c r="AH52" s="15"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
       <x:c r="A53" s="12"/>
@@ -2089,10 +2309,10 @@
       <x:c r="F53" s="14"/>
       <x:c r="G53" s="14"/>
       <x:c r="H53" s="14"/>
-      <x:c r="I53" s="13"/>
-      <x:c r="J53" s="15"/>
-      <x:c r="K53" s="13"/>
-      <x:c r="L53" s="15"/>
+      <x:c r="I53" s="14"/>
+      <x:c r="J53" s="14"/>
+      <x:c r="K53" s="14"/>
+      <x:c r="L53" s="14"/>
       <x:c r="M53" s="13"/>
       <x:c r="N53" s="15"/>
       <x:c r="O53" s="13"/>
@@ -2111,6 +2331,10 @@
       <x:c r="AB53" s="15"/>
       <x:c r="AC53" s="13"/>
       <x:c r="AD53" s="15"/>
+      <x:c r="AE53" s="13"/>
+      <x:c r="AF53" s="15"/>
+      <x:c r="AG53" s="13"/>
+      <x:c r="AH53" s="15"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2120,7 +2344,11 @@
     <x:mergeCell ref="D1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="H1:H2"/>
-    <x:mergeCell ref="I1:AD1"/>
+    <x:mergeCell ref="I1:I2"/>
+    <x:mergeCell ref="J1:J2"/>
+    <x:mergeCell ref="K1:K2"/>
+    <x:mergeCell ref="L1:L2"/>
+    <x:mergeCell ref="M1:AH1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
